--- a/branches/dependabot/github_actions/dev/actions-b6b232b097/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-b6b232b097/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T00:04:28+00:00</t>
+    <t>2026-09-09T14:31:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
